--- a/static/template.xlsx
+++ b/static/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AkshayKargutkar\Desktop\Tricks\CDN Links\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AkshayKargutkar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A3B2B6-395D-4894-9BE7-C8F5063F9E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9444A0-1440-4EC8-BB9D-12B67D5EA99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="759" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8743" tabRatio="759" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="170">
   <si>
     <t>Master ID</t>
   </si>
@@ -90,127 +90,7 @@
     <t>SDS URL</t>
   </si>
   <si>
-    <t>P0U19WCG</t>
-  </si>
-  <si>
     <t>DE</t>
-  </si>
-  <si>
-    <t>B0FR82JCDB</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/816+4-b6UzL._AC_SL1500_.jpg</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81wgbEfMqrL._AC_SL1500_.jpg</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81EoOviYi0L._AC_SL1500_.jpg</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81JUaO9uYML._AC_SL1500_.jpg</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81fQWY+FYML._AC_SL1500_.jpg</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81jnPTBLtvL._AC_SL1500_.jpg</t>
-  </si>
-  <si>
-    <t>P0A6HRWA</t>
-  </si>
-  <si>
-    <t>B0FR6T7M2Y</t>
-  </si>
-  <si>
-    <t>P0FCL88P</t>
-  </si>
-  <si>
-    <t>B0FR7JD1T6</t>
-  </si>
-  <si>
-    <t>P0TH0GIE</t>
-  </si>
-  <si>
-    <t>B0FR7JQB4M</t>
-  </si>
-  <si>
-    <t>P0Q0M0LO</t>
-  </si>
-  <si>
-    <t>B0FR7GPGWH</t>
-  </si>
-  <si>
-    <t>P0XJCMQ8</t>
-  </si>
-  <si>
-    <t>B0FR7YJVCK</t>
-  </si>
-  <si>
-    <t>P0PM2L7D</t>
-  </si>
-  <si>
-    <t>B0FR7F5CM8</t>
-  </si>
-  <si>
-    <t>P0F2QTJ7</t>
-  </si>
-  <si>
-    <t>B0FR7JYRFL</t>
-  </si>
-  <si>
-    <t>P0OTABBT</t>
-  </si>
-  <si>
-    <t>B0FR6ZV4LW</t>
-  </si>
-  <si>
-    <t>P0BJU3QZ</t>
-  </si>
-  <si>
-    <t>B0FR7FZPZX</t>
-  </si>
-  <si>
-    <t>P0SL9EDO</t>
-  </si>
-  <si>
-    <t>B0FR7ZCBVK</t>
-  </si>
-  <si>
-    <t>P0AU5D2Q</t>
-  </si>
-  <si>
-    <t>B0FR81DXFK</t>
-  </si>
-  <si>
-    <t>P0RPEU8P</t>
-  </si>
-  <si>
-    <t>B0FR7FJNHJ</t>
-  </si>
-  <si>
-    <t>P0VDPPUK</t>
-  </si>
-  <si>
-    <t>B0FR7LCLL5</t>
-  </si>
-  <si>
-    <t>P0K3PJEN</t>
-  </si>
-  <si>
-    <t>B0FR7G8TSZ</t>
-  </si>
-  <si>
-    <t>P0BM64GW</t>
-  </si>
-  <si>
-    <t>B0FR721N9T</t>
-  </si>
-  <si>
-    <t>P0POFCHG</t>
-  </si>
-  <si>
-    <t>B0FR7KM4WW</t>
   </si>
   <si>
     <t>Media Stack Group</t>
@@ -1190,196 +1070,196 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="113.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="113.69140625" customWidth="1"/>
+    <col min="2" max="2" width="14.3828125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="20.7" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2"/>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="C23" t="s">
         <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1394,19 +1274,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:V106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.15234375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.53515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="9.84375" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.84375" style="12" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.3828125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1474,829 +1354,320 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="5">
-        <v>931042</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>24</v>
-      </c>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E2" s="13"/>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="5">
-        <v>931043</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>32</v>
-      </c>
+      <c r="I2" s="13"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E3" s="13"/>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="5">
-        <v>931052</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>34</v>
-      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E4" s="13"/>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="5">
-        <v>931053</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>36</v>
-      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E5" s="13"/>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="5">
-        <v>931061</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>38</v>
-      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E6" s="13"/>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="5">
-        <v>931063</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>40</v>
-      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E7" s="13"/>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="5">
-        <v>931062</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>42</v>
-      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E8" s="13"/>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="5">
-        <v>931064</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>44</v>
-      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E9" s="13"/>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="5">
-        <v>931072</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>46</v>
-      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E10" s="13"/>
-      <c r="F10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="5">
-        <v>931071</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>48</v>
-      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E11" s="13"/>
-      <c r="F11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="5">
-        <v>931073</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>50</v>
-      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E12" s="13"/>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" t="s">
-        <v>29</v>
-      </c>
-      <c r="K12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="5">
-        <v>931081</v>
-      </c>
-      <c r="C13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>52</v>
-      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E13" s="13"/>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" t="s">
-        <v>29</v>
-      </c>
-      <c r="K13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="5">
-        <v>931080</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>54</v>
-      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E14" s="13"/>
-      <c r="F14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="5">
-        <v>931082</v>
-      </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>56</v>
-      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E15" s="13"/>
-      <c r="F15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="5">
-        <v>931091</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>58</v>
-      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.4">
       <c r="E16" s="13"/>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" t="s">
-        <v>29</v>
-      </c>
-      <c r="K16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="5">
-        <v>931090</v>
-      </c>
-      <c r="C17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>60</v>
-      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E17" s="13"/>
-      <c r="F17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" t="s">
-        <v>29</v>
-      </c>
-      <c r="K17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="5">
-        <v>931092</v>
-      </c>
-      <c r="C18" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>62</v>
-      </c>
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E18" s="13"/>
-      <c r="F18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E19" s="13"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E21" s="13"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E23" s="13"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E24" s="13"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E25" s="13"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E26" s="13"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E27" s="13"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E28" s="13"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E29" s="13"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E30" s="13"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E31" s="13"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E32" s="13"/>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E33" s="13"/>
     </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E34" s="13"/>
     </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E35" s="13"/>
     </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E36" s="13"/>
     </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E37" s="13"/>
     </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E38" s="13"/>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E39" s="13"/>
     </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E40" s="13"/>
     </row>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E41" s="13"/>
     </row>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E42" s="13"/>
     </row>
-    <row r="43" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E43" s="13"/>
     </row>
-    <row r="44" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E44" s="13"/>
     </row>
-    <row r="45" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E45" s="13"/>
     </row>
-    <row r="46" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E46" s="13"/>
     </row>
-    <row r="47" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E47" s="13"/>
     </row>
-    <row r="48" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E48" s="13"/>
     </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E49" s="13"/>
     </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E50" s="13"/>
     </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E51" s="13"/>
     </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E52" s="13"/>
     </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E53" s="13"/>
     </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E54" s="13"/>
     </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E55" s="13"/>
     </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E56" s="13"/>
     </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E57" s="13"/>
     </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E58" s="13"/>
     </row>
-    <row r="59" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E59" s="13"/>
     </row>
-    <row r="60" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E60" s="13"/>
     </row>
-    <row r="61" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E61" s="13"/>
     </row>
-    <row r="62" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E62" s="13"/>
     </row>
-    <row r="63" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E63" s="13"/>
     </row>
-    <row r="64" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E64" s="13"/>
     </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E65" s="13"/>
     </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E66" s="13"/>
     </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E67" s="13"/>
     </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E68" s="13"/>
     </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E69" s="13"/>
     </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E70" s="13"/>
     </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E71" s="13"/>
     </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E72" s="13"/>
     </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E73" s="13"/>
     </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E74" s="13"/>
     </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E75" s="13"/>
     </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E76" s="13"/>
     </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E77" s="13"/>
     </row>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E78" s="13"/>
     </row>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E79" s="13"/>
     </row>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E80" s="13"/>
     </row>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E81" s="13"/>
     </row>
-    <row r="82" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E82" s="13"/>
     </row>
-    <row r="83" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E83" s="13"/>
     </row>
-    <row r="84" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E84" s="13"/>
     </row>
-    <row r="85" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E85" s="13"/>
     </row>
-    <row r="86" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E86" s="13"/>
     </row>
-    <row r="87" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E87" s="13"/>
     </row>
-    <row r="88" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E88" s="13"/>
     </row>
-    <row r="89" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E89" s="13"/>
     </row>
-    <row r="90" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E90" s="13"/>
     </row>
-    <row r="91" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E91" s="13"/>
     </row>
-    <row r="92" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E92" s="13"/>
     </row>
-    <row r="93" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E93" s="13"/>
     </row>
-    <row r="94" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E94" s="13"/>
     </row>
-    <row r="95" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E95" s="13"/>
     </row>
-    <row r="96" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E96" s="13"/>
     </row>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E97" s="13"/>
     </row>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E98" s="13"/>
     </row>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E99" s="13"/>
     </row>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E100" s="13"/>
     </row>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E101" s="13"/>
     </row>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E102" s="13"/>
     </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E103" s="13"/>
     </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E104" s="13"/>
     </row>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E105" s="13"/>
     </row>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E106" s="13"/>
     </row>
   </sheetData>
@@ -2309,532 +1680,532 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:C103"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.140625" customWidth="1"/>
+    <col min="1" max="1" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.3828125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.15234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B32" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B36" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B37" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B38" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B39" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="3" t="s">
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B40" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="3" t="s">
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B41" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B42" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B43" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B44" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B45" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B46" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B47" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B48" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B49" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B50" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B51" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B52" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B53" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B54" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B55" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B56" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B57" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B58" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B59" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B60" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B61" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B62" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B63" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
+    <row r="64" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B64" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B65" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B66" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B67" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B68" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B69" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B70" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B71" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B72" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B73" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B74" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B75" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B76" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
+    <row r="77" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B77" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B78" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B79" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B80" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B81" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B82" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B83" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B84" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B85" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
+    <row r="86" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B86" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B87" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B88" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
+    <row r="89" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B89" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B90" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B91" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
+    <row r="92" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B92" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B93" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
+    <row r="94" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B94" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B95" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B96" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" t="s">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B97" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B98" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B99" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B100" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B101" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B62" t="s">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B102" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B103" t="s">
         <v>169</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B64" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B72" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B74" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B75" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B85" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B86" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B92" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B94" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B95" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B97" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B99" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B100" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B101" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B102" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
-        <v>209</v>
       </c>
     </row>
   </sheetData>
